--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.87.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.87.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.87.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.87.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -594,27 +594,31 @@
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>L8: suspicious token(s): 1845ject (letter/digit mix) | localized OCR phrase divergence vs other OCR: "ver" vs "n 1845ject taken and no receiver" :: Â°n 1845ject. taken, and no receiver appointed, under the decree, nor</t>
+          <t>L8: suspicious token(s): 1845ject (letter/digit mix) | localized OCR phrase divergence vs other OCR: "ver" vs "n 1845ject taken and no receiver" :: °n 1845ject. taken, and no receiver appointed, under the decree, nor</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>L8: suspicious token(s): 1845ject (letter/digit mix) | localized OCR phrase divergence vs other OCR: "ver" vs "n 1845ject taken and no receiver" :: Â°n 1845ject. taken, and no receiver appointed, under the decree, nor</t>
+          <t>L8: suspicious token(s): 1845ject (letter/digit mix) | localized OCR phrase divergence vs other OCR: "ver" vs "n 1845ject taken and no receiver" :: °n 1845ject. taken, and no receiver appointed, under the decree, nor</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: English Orders here adopted, is as follows : â€˜No proceeding is to be</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]PROCEEDINGS TO HEAR CAUSE " PRO CONFESSO."</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]PROCEEDINGS TO HEAR CAUSE " PRO CONFESSO."</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L3: symbol-only separator/garbage line :: 1845.</t>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,14 +664,10 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œUpon the execution of an at</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: such service, that the Bill may â€˜be takenpro confesso</t>
-        </is>
-      </c>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -713,11 +713,7 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: r.â€�</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
@@ -755,7 +751,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -817,7 +813,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -969,12 +965,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1017,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1055,7 +1051,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1204,7 +1200,7 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L110: symbol-only separator/garbage line :: 77.</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr"/>
@@ -1245,7 +1241,11 @@
       <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
-      <c r="N16" s="1" t="inlineStr"/>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>L109: isolated marker/symbol line :: r.”</t>
+        </is>
+      </c>
       <c r="O16" s="1" t="inlineStr"/>
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr"/>
@@ -1284,7 +1284,11 @@
       <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
-      <c r="N17" s="1" t="inlineStr"/>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>L110: symbol-only separator/garbage line :: 77.</t>
+        </is>
+      </c>
       <c r="O17" s="1" t="inlineStr"/>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
